--- a/base_completa.xlsx
+++ b/base_completa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ander\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ander\Documents\GitHub\Proyecto-Lineales-avanzados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A5F159-DCBD-4C68-A0A9-7AC5777AB4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{323C50BF-CEDC-4D8A-B737-12D8A7E65FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{645CD550-06DF-45D9-AEB3-94C9F1B9CD95}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{645CD550-06DF-45D9-AEB3-94C9F1B9CD95}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Semestre</t>
-  </si>
-  <si>
-    <t>us</t>
   </si>
   <si>
     <t>intentados</t>
@@ -246,6 +243,9 @@
   </si>
   <si>
     <t>s28</t>
+  </si>
+  <si>
+    <t>sus</t>
   </si>
 </sst>
 </file>
@@ -751,21 +751,21 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4">
         <v>0.38194444444444442</v>
@@ -781,7 +781,7 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2">
         <v>27.5</v>
@@ -792,13 +792,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>0.43680555555555556</v>
@@ -814,7 +814,7 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>32.5</v>
@@ -825,13 +825,13 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4">
         <v>0.44791666666666669</v>
@@ -847,7 +847,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4">
         <v>85</v>
@@ -858,13 +858,13 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="4">
         <v>0.47916666666666669</v>
@@ -880,7 +880,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I5">
         <v>85</v>
@@ -891,13 +891,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4">
         <v>0.38541666666666669</v>
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I6">
         <v>87.5</v>
@@ -924,13 +924,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="4">
         <v>0.42222222222222222</v>
@@ -946,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I7">
         <v>85</v>
@@ -957,13 +957,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4">
         <v>0.40694444444444444</v>
@@ -979,7 +979,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8">
         <v>87.5</v>
@@ -990,13 +990,13 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="4">
         <v>0.44583333333333336</v>
@@ -1012,7 +1012,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9">
         <v>82.5</v>
@@ -1023,13 +1023,13 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="4">
         <v>0.3840277777777778</v>
@@ -1045,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10">
         <v>92.5</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="4">
         <v>0.40069444444444446</v>
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I11">
         <v>77.5</v>
@@ -1089,13 +1089,13 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="4">
         <v>0.4201388888888889</v>
@@ -1111,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I12">
         <v>72.5</v>
@@ -1122,13 +1122,13 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>4</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4">
         <v>0.44583333333333336</v>
@@ -1144,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I13">
         <v>57.5</v>
@@ -1155,13 +1155,13 @@
     </row>
     <row r="14" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="8">
         <v>1</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="6">
         <v>0.38541666666666669</v>
@@ -1177,7 +1177,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14" s="8">
         <v>4</v>
@@ -1188,13 +1188,13 @@
     </row>
     <row r="15" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="8">
         <v>2</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="6">
         <v>0.40416666666666667</v>
@@ -1210,7 +1210,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J15" s="8">
         <v>3</v>
@@ -1221,13 +1221,13 @@
     </row>
     <row r="16" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="8">
         <v>3</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="6">
         <v>0.41319444444444442</v>
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J16" s="8">
         <v>4</v>
@@ -1254,13 +1254,13 @@
     </row>
     <row r="17" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="8">
         <v>4</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="6">
         <v>0.43055555555555558</v>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J17" s="8">
         <v>4</v>
@@ -1287,13 +1287,13 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="4">
         <v>0.39027777777777778</v>
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -1320,13 +1320,13 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" s="4">
         <v>0.46527777777777779</v>
@@ -1342,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="4">
         <v>0.41458333333333336</v>
@@ -1375,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I20">
         <v>85</v>
@@ -1386,13 +1386,13 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" s="4">
         <v>0.44374999999999998</v>
@@ -1408,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I21">
         <v>85</v>
@@ -1419,13 +1419,13 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" s="4">
         <v>0.39027777777777778</v>
@@ -1441,7 +1441,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I22">
         <v>87.5</v>
@@ -1452,13 +1452,13 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" s="4">
         <v>0.40277777777777779</v>
@@ -1474,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I23">
         <v>97.5</v>
@@ -1485,13 +1485,13 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="4">
         <v>0.41458333333333336</v>
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I24">
         <v>90</v>
@@ -1518,13 +1518,13 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" s="4">
         <v>0.42916666666666664</v>
@@ -1540,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I25">
         <v>97.5</v>
@@ -1551,13 +1551,13 @@
     </row>
     <row r="26" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="8">
         <v>1</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="6">
         <v>0.3923611111111111</v>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J26" s="8">
         <v>4</v>
@@ -1584,13 +1584,13 @@
     </row>
     <row r="27" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="8">
         <v>2</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" s="6">
         <v>0.43472222222222223</v>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J27" s="8">
         <v>3</v>
@@ -1617,13 +1617,13 @@
     </row>
     <row r="28" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="8">
         <v>3</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" s="6">
         <v>0.47222222222222221</v>
@@ -1639,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J28" s="8">
         <v>4</v>
@@ -1650,13 +1650,13 @@
     </row>
     <row r="29" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="8">
         <v>4</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" s="6">
         <v>0.4513888888888889</v>
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J29" s="8">
         <v>4</v>
@@ -1683,13 +1683,13 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" s="4">
         <v>0.39583333333333331</v>
@@ -1705,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I30">
         <v>77.5</v>
@@ -1716,13 +1716,13 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="4">
         <v>0.41319444444444442</v>
@@ -1738,7 +1738,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I31" s="8">
         <v>92.5</v>
@@ -1749,13 +1749,13 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32">
         <v>3</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" s="4">
         <v>0.44444444444444442</v>
@@ -1771,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I32">
         <v>92.5</v>
@@ -1782,13 +1782,13 @@
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" s="4">
         <v>0.47222222222222221</v>
@@ -1804,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I33">
         <v>87.5</v>
@@ -1815,13 +1815,13 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" s="4">
         <v>0.3888888888888889</v>
@@ -1837,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I34">
         <v>80</v>
@@ -1848,13 +1848,13 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="4">
         <v>0.41944444444444445</v>
@@ -1870,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I35">
         <v>87.5</v>
@@ -1881,13 +1881,13 @@
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B36">
         <v>3</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D36" s="4">
         <v>0.43819444444444444</v>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I36">
         <v>85</v>
@@ -1914,13 +1914,13 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" s="4">
         <v>0.46250000000000002</v>
@@ -1936,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I37">
         <v>87.5</v>
@@ -1947,13 +1947,13 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" s="4">
         <v>0.3923611111111111</v>
@@ -1969,7 +1969,7 @@
         <v>3</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I38">
         <v>82.5</v>
@@ -1980,13 +1980,13 @@
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D39" s="4">
         <v>0.46041666666666664</v>
@@ -2002,7 +2002,7 @@
         <v>3</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I39">
         <v>97.5</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40">
         <v>3</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="4">
         <v>0.4236111111111111</v>
@@ -2035,7 +2035,7 @@
         <v>3</v>
       </c>
       <c r="H40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40">
         <v>62.5</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D41" s="4">
         <v>0.47222222222222221</v>
@@ -2068,7 +2068,7 @@
         <v>3</v>
       </c>
       <c r="H41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I41">
         <v>70</v>
@@ -2079,13 +2079,13 @@
     </row>
     <row r="42" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" s="12">
         <v>1</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D42" s="14">
         <v>0.40277777777777779</v>
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I42" s="12">
         <v>55</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="43" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B43" s="12">
         <v>2</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D43" s="14">
         <v>0.42916666666666664</v>
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I43" s="12">
         <v>55</v>
@@ -2151,13 +2151,13 @@
     </row>
     <row r="44" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B44" s="12">
         <v>3</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D44" s="14">
         <v>0.44791666666666669</v>
@@ -2173,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J44" s="12">
         <v>4</v>
@@ -2184,13 +2184,13 @@
     </row>
     <row r="45" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B45" s="12">
         <v>4</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D45" s="14">
         <v>0.46527777777777779</v>
@@ -2206,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J45" s="12">
         <v>4</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="46" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B46" s="12">
         <v>1</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D46" s="14">
         <v>0.39583333333333331</v>
@@ -2239,7 +2239,7 @@
         <v>5</v>
       </c>
       <c r="H46" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I46" s="12">
         <v>57.5</v>
@@ -2253,13 +2253,13 @@
     </row>
     <row r="47" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="12">
         <v>2</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D47" s="14">
         <v>0.43055555555555558</v>
@@ -2275,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I47" s="12">
         <v>85</v>
@@ -2289,13 +2289,13 @@
     </row>
     <row r="48" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" s="12">
         <v>3</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="14">
         <v>0.45</v>
@@ -2311,7 +2311,7 @@
         <v>5</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J48" s="12">
         <v>4</v>
@@ -2322,13 +2322,13 @@
     </row>
     <row r="49" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" s="12">
         <v>4</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" s="14">
         <v>0.45694444444444443</v>
@@ -2344,7 +2344,7 @@
         <v>5</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J49" s="12">
         <v>4</v>
@@ -2355,13 +2355,13 @@
     </row>
     <row r="50" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B50" s="12">
         <v>1</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D50" s="14">
         <v>0.4375</v>
@@ -2377,7 +2377,7 @@
         <v>2</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J50" s="12">
         <v>3</v>
@@ -2385,13 +2385,13 @@
     </row>
     <row r="51" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51" s="12">
         <v>2</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" s="16"/>
       <c r="E51" s="16"/>
@@ -2403,7 +2403,7 @@
         <v>2</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J51" s="12">
         <v>4</v>
@@ -2411,13 +2411,13 @@
     </row>
     <row r="52" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" s="12">
         <v>3</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" s="14">
         <v>0.47708333333333336</v>
@@ -2433,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J52" s="12">
         <v>2</v>
@@ -2441,13 +2441,13 @@
     </row>
     <row r="53" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B53" s="12">
         <v>4</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
@@ -2459,7 +2459,7 @@
         <v>2</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J53" s="12">
         <v>4</v>
@@ -2467,13 +2467,13 @@
     </row>
     <row r="54" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B54" s="12">
         <v>1</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D54" s="14">
         <v>0.3888888888888889</v>
@@ -2489,7 +2489,7 @@
         <v>3</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I54" s="12">
         <v>80</v>
@@ -2500,13 +2500,13 @@
     </row>
     <row r="55" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B55" s="12">
         <v>2</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D55" s="14">
         <v>0.46805555555555556</v>
@@ -2522,7 +2522,7 @@
         <v>3</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J55" s="12">
         <v>1</v>
@@ -2530,13 +2530,13 @@
     </row>
     <row r="56" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B56" s="12">
         <v>3</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
@@ -2548,7 +2548,7 @@
         <v>3</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J56" s="12">
         <v>4</v>
@@ -2556,13 +2556,13 @@
     </row>
     <row r="57" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B57" s="12">
         <v>4</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
@@ -2574,7 +2574,7 @@
         <v>3</v>
       </c>
       <c r="H57" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J57" s="12">
         <v>2</v>
@@ -2582,13 +2582,13 @@
     </row>
     <row r="58" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B58" s="12">
         <v>1</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" s="14">
         <v>0.40625</v>
@@ -2604,7 +2604,7 @@
         <v>5</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J58" s="12">
         <v>4</v>
@@ -2612,13 +2612,13 @@
     </row>
     <row r="59" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B59" s="12">
         <v>2</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
@@ -2630,7 +2630,7 @@
         <v>5</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J59" s="12">
         <v>4</v>
@@ -2638,13 +2638,13 @@
     </row>
     <row r="60" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B60" s="12">
         <v>3</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
@@ -2656,7 +2656,7 @@
         <v>5</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J60" s="12">
         <v>4</v>
@@ -2664,13 +2664,13 @@
     </row>
     <row r="61" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B61" s="12">
         <v>4</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
@@ -2682,7 +2682,7 @@
         <v>5</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J61" s="12">
         <v>4</v>
@@ -2690,13 +2690,13 @@
     </row>
     <row r="62" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B62" s="12">
         <v>1</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D62" s="14">
         <v>0.55277777777777781</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J62" s="12">
         <v>2</v>
@@ -2720,13 +2720,13 @@
     </row>
     <row r="63" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B63" s="12">
         <v>2</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D63" s="14">
         <v>0.57708333333333328</v>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I63" s="12">
         <v>90</v>
@@ -2753,13 +2753,13 @@
     </row>
     <row r="64" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B64" s="12">
         <v>3</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D64" s="14">
         <v>0.59097222222222223</v>
@@ -2775,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I64" s="12">
         <v>50</v>
@@ -2786,13 +2786,13 @@
     </row>
     <row r="65" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65" s="12">
         <v>4</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D65" s="14">
         <v>0.61388888888888893</v>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I65" s="12">
         <v>40</v>
@@ -2819,13 +2819,13 @@
     </row>
     <row r="66" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B66" s="12">
         <v>1</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D66" s="14">
         <v>0.43611111111111112</v>
@@ -2841,7 +2841,7 @@
         <v>3</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I66" s="12">
         <v>50</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="67" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B67" s="12">
         <v>2</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D67" s="14">
         <v>0.45277777777777778</v>
@@ -2874,7 +2874,7 @@
         <v>3</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I67" s="12">
         <v>65</v>
@@ -2885,13 +2885,13 @@
     </row>
     <row r="68" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B68" s="12">
         <v>3</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D68" s="14">
         <v>0.48958333333333331</v>
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J68" s="12">
         <v>2</v>
@@ -2915,13 +2915,13 @@
     </row>
     <row r="69" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B69" s="12">
         <v>4</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" s="16"/>
       <c r="E69" s="16"/>
@@ -2933,7 +2933,7 @@
         <v>3</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J69" s="12">
         <v>4</v>
@@ -2941,13 +2941,13 @@
     </row>
     <row r="70" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B70" s="12">
         <v>1</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D70" s="14">
         <v>0.42777777777777776</v>
@@ -2963,7 +2963,7 @@
         <v>5</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I70" s="12">
         <v>67.5</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="71" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B71" s="12">
         <v>2</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D71" s="14">
         <v>0.4597222222222222</v>
@@ -2999,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I71" s="12">
         <v>90</v>
@@ -3013,13 +3013,13 @@
     </row>
     <row r="72" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B72" s="12">
         <v>3</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D72" s="14">
         <v>0.47361111111111109</v>
@@ -3035,7 +3035,7 @@
         <v>5</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J72" s="12">
         <v>4</v>
@@ -3046,13 +3046,13 @@
     </row>
     <row r="73" spans="1:18" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B73" s="12">
         <v>4</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D73" s="14">
         <v>0.4826388888888889</v>
@@ -3068,7 +3068,7 @@
         <v>5</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J73" s="12">
         <v>4</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D74" s="4">
         <v>0.42430555555555555</v>
@@ -3101,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I74">
         <v>75</v>
@@ -3112,13 +3112,13 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D75" s="4">
         <v>0.44305555555555554</v>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I75">
         <v>92.5</v>
@@ -3145,13 +3145,13 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B76">
         <v>3</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D76" s="4">
         <v>0.45833333333333331</v>
@@ -3167,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I76">
         <v>95</v>
@@ -3178,13 +3178,13 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B77">
         <v>4</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" s="4">
         <v>0.4777777777777778</v>
@@ -3200,7 +3200,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I77">
         <v>72.5</v>
@@ -3211,13 +3211,13 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D78" s="4">
         <v>0.54722222222222228</v>
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I78">
         <v>97.5</v>
@@ -3244,13 +3244,13 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D79" s="4">
         <v>0.5625</v>
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I79">
         <v>100</v>
@@ -3277,13 +3277,13 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B80">
         <v>3</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D80" s="4">
         <v>0.58888888888888891</v>
@@ -3299,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80">
         <v>100</v>
@@ -3310,13 +3310,13 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B81">
         <v>4</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D81" s="4">
         <v>0.60555555555555551</v>
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I81">
         <v>100</v>
@@ -3343,13 +3343,13 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D82" s="4">
         <v>0.55347222222222225</v>
@@ -3365,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I82">
         <v>77.5</v>
@@ -3376,13 +3376,13 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D83" s="4">
         <v>0.5708333333333333</v>
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I83">
         <v>92.5</v>
@@ -3409,13 +3409,13 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84">
         <v>3</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D84" s="4">
         <v>0.60624999999999996</v>
@@ -3431,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I84">
         <v>90</v>
@@ -3442,13 +3442,13 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85">
         <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D85" s="4">
         <v>0.62986111111111109</v>
@@ -3464,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I85">
         <v>87.5</v>
@@ -3475,13 +3475,13 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D86" s="4">
         <v>0.55555555555555558</v>
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I86">
         <v>97.5</v>
@@ -3508,13 +3508,13 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D87" s="4">
         <v>0.58125000000000004</v>
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I87">
         <v>90</v>
@@ -3541,13 +3541,13 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88">
         <v>3</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D88" s="4">
         <v>0.6020833333333333</v>
@@ -3563,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I88">
         <v>70</v>
@@ -3574,13 +3574,13 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B89">
         <v>4</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D89" s="4">
         <v>0.6118055555555556</v>
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I89">
         <v>95</v>
@@ -3607,13 +3607,13 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D90" s="4">
         <v>0.55694444444444446</v>
@@ -3629,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I90">
         <v>82.5</v>
@@ -3640,13 +3640,13 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D91" s="4">
         <v>0.56666666666666665</v>
@@ -3662,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I91">
         <v>85</v>
@@ -3673,13 +3673,13 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D92" s="4">
         <v>0.57152777777777775</v>
@@ -3695,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I92">
         <v>82.5</v>
@@ -3706,13 +3706,13 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B93">
         <v>4</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D93" s="4">
         <v>0.6</v>
@@ -3728,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I93">
         <v>90</v>
@@ -3739,13 +3739,13 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D94" s="4">
         <v>0.55555555555555558</v>
@@ -3761,7 +3761,7 @@
         <v>2</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I94">
         <v>55</v>
@@ -3772,13 +3772,13 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D95" s="4">
         <v>0.59861111111111109</v>
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I95">
         <v>67.5</v>
@@ -3805,13 +3805,13 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D96" s="4">
         <v>0.62013888888888891</v>
@@ -3827,7 +3827,7 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I96">
         <v>77.5</v>
@@ -3838,13 +3838,13 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B97">
         <v>4</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D97" s="4">
         <v>0.62916666666666665</v>
@@ -3860,7 +3860,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I97">
         <v>70</v>
@@ -3871,13 +3871,13 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D98" s="4">
         <v>0.55277777777777781</v>
@@ -3893,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="H98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I98">
         <v>95</v>
@@ -3904,13 +3904,13 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D99" s="4">
         <v>0.62986111111111109</v>
@@ -3926,7 +3926,7 @@
         <v>3</v>
       </c>
       <c r="H99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I99">
         <v>87.5</v>
@@ -3937,13 +3937,13 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D100" s="4">
         <v>0.65347222222222223</v>
@@ -3959,7 +3959,7 @@
         <v>3</v>
       </c>
       <c r="H100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I100">
         <v>87.5</v>
@@ -3970,13 +3970,13 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B101">
         <v>4</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D101" s="4">
         <v>0.59722222222222221</v>
@@ -3992,7 +3992,7 @@
         <v>3</v>
       </c>
       <c r="H101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I101">
         <v>87.5</v>
@@ -4003,13 +4003,13 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D102" s="4">
         <v>0.55555555555555558</v>
@@ -4025,7 +4025,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I102">
         <v>80</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D103" s="4">
         <v>0.57291666666666663</v>
@@ -4058,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I103">
         <v>80</v>
@@ -4069,13 +4069,13 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" s="4">
         <v>0.58680555555555558</v>
@@ -4091,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I104">
         <v>85</v>
@@ -4102,13 +4102,13 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B105">
         <v>4</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D105" s="4">
         <v>0.60416666666666663</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I105">
         <v>80</v>
@@ -4135,13 +4135,13 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D106" s="4">
         <v>0.55347222222222225</v>
@@ -4157,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I106">
         <v>85</v>
@@ -4168,13 +4168,13 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D107" s="4">
         <v>0.5805555555555556</v>
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I107">
         <v>87.5</v>
@@ -4201,13 +4201,13 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B108">
         <v>3</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D108" s="4">
         <v>0.63263888888888886</v>
@@ -4223,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I108">
         <v>57.5</v>
@@ -4234,13 +4234,13 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B109">
         <v>4</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D109" s="4">
         <v>0.6020833333333333</v>
@@ -4256,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I109">
         <v>52.5</v>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D110" s="4">
         <v>0.56944444444444442</v>
@@ -4289,7 +4289,7 @@
         <v>2</v>
       </c>
       <c r="H110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I110">
         <v>52.5</v>
@@ -4300,13 +4300,13 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D111" s="4">
         <v>0.59652777777777777</v>
@@ -4322,7 +4322,7 @@
         <v>2</v>
       </c>
       <c r="H111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I111">
         <v>45</v>
@@ -4333,13 +4333,13 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B112">
         <v>3</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D112" s="4">
         <v>0.66388888888888886</v>
@@ -4355,7 +4355,7 @@
         <v>2</v>
       </c>
       <c r="H112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I112">
         <v>62.5</v>
@@ -4366,13 +4366,13 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B113">
         <v>4</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D113" s="4">
         <v>0.68680555555555556</v>
@@ -4388,7 +4388,7 @@
         <v>2</v>
       </c>
       <c r="H113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I113">
         <v>50</v>
@@ -4399,13 +4399,13 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D114" s="4">
         <v>0.39097222222222222</v>
@@ -4421,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J114">
         <v>4</v>
@@ -4429,13 +4429,13 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D115" s="4">
         <v>0.43125000000000002</v>
@@ -4451,7 +4451,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I115">
         <v>65</v>
@@ -4462,13 +4462,13 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -4480,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I116">
         <v>47.5</v>
@@ -4491,13 +4491,13 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B117">
         <v>4</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -4509,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J117">
         <v>2</v>
@@ -4517,13 +4517,13 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D118" s="4">
         <v>0.37361111111111112</v>
@@ -4539,7 +4539,7 @@
         <v>3</v>
       </c>
       <c r="H118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I118">
         <v>77.5</v>
@@ -4550,13 +4550,13 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D119" s="4">
         <v>0.42708333333333331</v>
@@ -4572,7 +4572,7 @@
         <v>3</v>
       </c>
       <c r="H119" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I119">
         <v>85</v>
@@ -4583,13 +4583,13 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D120" s="4">
         <v>0.4548611111111111</v>
@@ -4605,7 +4605,7 @@
         <v>3</v>
       </c>
       <c r="H120" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I120">
         <v>70</v>
@@ -4616,13 +4616,13 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D121" s="4">
         <v>0.49791666666666667</v>
@@ -4638,7 +4638,7 @@
         <v>3</v>
       </c>
       <c r="H121" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I121">
         <v>52.5</v>
@@ -4649,13 +4649,13 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D122" s="4">
         <v>0.375</v>
@@ -4671,7 +4671,7 @@
         <v>2</v>
       </c>
       <c r="H122" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I122">
         <v>60</v>
@@ -4682,13 +4682,13 @@
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D123" s="4">
         <v>0.38819444444444445</v>
@@ -4704,7 +4704,7 @@
         <v>2</v>
       </c>
       <c r="H123" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I123">
         <v>85</v>
@@ -4715,13 +4715,13 @@
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B124">
         <v>3</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D124" s="4">
         <v>0.40555555555555556</v>
@@ -4737,7 +4737,7 @@
         <v>2</v>
       </c>
       <c r="H124" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I124">
         <v>85</v>
@@ -4748,13 +4748,13 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D125" s="4">
         <v>0.42499999999999999</v>
@@ -4770,7 +4770,7 @@
         <v>2</v>
       </c>
       <c r="H125" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I125">
         <v>57.5</v>
@@ -4781,13 +4781,13 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D126" s="4">
         <v>0.38194444444444442</v>
@@ -4803,7 +4803,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I126">
         <v>82.5</v>
@@ -4814,13 +4814,13 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D127" s="4">
         <v>0.42499999999999999</v>
@@ -4836,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I127">
         <v>65</v>
@@ -4847,13 +4847,13 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -4865,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I128">
         <v>85</v>
@@ -4876,13 +4876,13 @@
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B129">
         <v>4</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -4894,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I129">
         <v>67.5</v>
@@ -4905,13 +4905,13 @@
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D130" s="4">
         <v>0.37708333333333333</v>
@@ -4927,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I130">
         <v>90</v>
@@ -4938,13 +4938,13 @@
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D131" s="4">
         <v>0.41666666666666669</v>
@@ -4960,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I131">
         <v>87.5</v>
@@ -4971,13 +4971,13 @@
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D132" s="4">
         <v>0.44236111111111109</v>
@@ -4993,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I132">
         <v>82.5</v>
@@ -5004,13 +5004,13 @@
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B133">
         <v>4</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D133" s="4">
         <v>0.48333333333333334</v>
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I133">
         <v>87.5</v>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D134" s="4">
         <v>0.38611111111111113</v>
@@ -5059,7 +5059,7 @@
         <v>3</v>
       </c>
       <c r="H134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I134">
         <v>95</v>
@@ -5070,13 +5070,13 @@
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B135">
         <v>2</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D135" s="4">
         <v>0.44374999999999998</v>
@@ -5092,7 +5092,7 @@
         <v>3</v>
       </c>
       <c r="H135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J135">
         <v>4</v>
@@ -5100,13 +5100,13 @@
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B136">
         <v>3</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D136" s="4">
         <v>0.46666666666666667</v>
@@ -5122,7 +5122,7 @@
         <v>3</v>
       </c>
       <c r="H136" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J136">
         <v>4</v>
@@ -5130,13 +5130,13 @@
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B137">
         <v>4</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D137" s="4">
         <v>0.49652777777777779</v>
@@ -5152,7 +5152,7 @@
         <v>3</v>
       </c>
       <c r="H137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J137">
         <v>3</v>
@@ -5160,13 +5160,13 @@
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D138" s="4">
         <v>0.3888888888888889</v>
@@ -5182,7 +5182,7 @@
         <v>3</v>
       </c>
       <c r="H138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I138">
         <v>95</v>
@@ -5193,13 +5193,13 @@
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D139" s="4">
         <v>0.44722222222222224</v>
@@ -5215,7 +5215,7 @@
         <v>3</v>
       </c>
       <c r="H139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I139">
         <v>70</v>
@@ -5226,13 +5226,13 @@
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B140">
         <v>3</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D140" s="4">
         <v>0.47638888888888886</v>
@@ -5248,7 +5248,7 @@
         <v>3</v>
       </c>
       <c r="H140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I140">
         <v>70</v>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B141">
         <v>4</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D141" s="4">
         <v>0.51180555555555551</v>
@@ -5281,7 +5281,7 @@
         <v>3</v>
       </c>
       <c r="H141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I141">
         <v>70</v>
@@ -5292,13 +5292,13 @@
     </row>
     <row r="142" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B142" s="12">
         <v>1</v>
       </c>
       <c r="C142" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D142" s="14">
         <v>0.37777777777777777</v>
@@ -5314,7 +5314,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I142" s="12">
         <v>72.5</v>
@@ -5325,13 +5325,13 @@
     </row>
     <row r="143" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B143" s="12">
         <v>2</v>
       </c>
       <c r="C143" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D143" s="14">
         <v>0.41944444444444445</v>
@@ -5347,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I143" s="12">
         <v>87.5</v>
@@ -5358,13 +5358,13 @@
     </row>
     <row r="144" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B144" s="12">
         <v>3</v>
       </c>
       <c r="C144" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D144" s="14">
         <v>0.4548611111111111</v>
@@ -5380,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="H144" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I144" s="12">
         <v>97.5</v>
@@ -5391,13 +5391,13 @@
     </row>
     <row r="145" spans="1:10" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B145" s="12">
         <v>4</v>
       </c>
       <c r="C145" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D145" s="14">
         <v>0.43125000000000002</v>
@@ -5413,7 +5413,7 @@
         <v>1</v>
       </c>
       <c r="H145" s="12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J145" s="12">
         <v>4</v>
@@ -5421,13 +5421,13 @@
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D146" s="4">
         <v>0.38055555555555554</v>
@@ -5443,7 +5443,7 @@
         <v>3</v>
       </c>
       <c r="H146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J146">
         <v>4</v>
@@ -5451,13 +5451,13 @@
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B147">
         <v>2</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D147" s="4">
         <v>0.41736111111111113</v>
@@ -5473,7 +5473,7 @@
         <v>3</v>
       </c>
       <c r="H147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J147">
         <v>4</v>
@@ -5481,13 +5481,13 @@
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B148">
         <v>3</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D148" s="4">
         <v>0.42916666666666664</v>
@@ -5503,7 +5503,7 @@
         <v>3</v>
       </c>
       <c r="H148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J148">
         <v>4</v>
@@ -5511,13 +5511,13 @@
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B149">
         <v>4</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D149" s="4">
         <v>0.47847222222222224</v>
@@ -5533,7 +5533,7 @@
         <v>3</v>
       </c>
       <c r="H149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J149">
         <v>4</v>
@@ -5541,13 +5541,13 @@
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D150" s="4">
         <v>0.38541666666666669</v>
@@ -5563,7 +5563,7 @@
         <v>2</v>
       </c>
       <c r="H150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I150">
         <v>50</v>
@@ -5574,13 +5574,13 @@
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B151">
         <v>2</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D151" s="4">
         <v>0.46180555555555558</v>
@@ -5596,7 +5596,7 @@
         <v>2</v>
       </c>
       <c r="H151" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J151">
         <v>4</v>
@@ -5604,13 +5604,13 @@
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -5622,7 +5622,7 @@
         <v>2</v>
       </c>
       <c r="H152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J152">
         <v>4</v>
@@ -5630,13 +5630,13 @@
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -5648,7 +5648,7 @@
         <v>2</v>
       </c>
       <c r="H153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I153">
         <v>40</v>
@@ -5659,13 +5659,13 @@
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D154" s="4">
         <v>0.38263888888888886</v>
@@ -5681,7 +5681,7 @@
         <v>3</v>
       </c>
       <c r="H154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I154">
         <v>47.5</v>
@@ -5692,13 +5692,13 @@
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B155">
         <v>2</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D155" s="4">
         <v>0.45277777777777778</v>
@@ -5714,7 +5714,7 @@
         <v>3</v>
       </c>
       <c r="H155" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J155">
         <v>4</v>
@@ -5722,13 +5722,13 @@
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B156">
         <v>3</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D156" s="4">
         <v>0.47222222222222221</v>
@@ -5744,7 +5744,7 @@
         <v>3</v>
       </c>
       <c r="H156" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I156">
         <v>67.5</v>
@@ -5755,13 +5755,13 @@
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B157">
         <v>4</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -5773,7 +5773,7 @@
         <v>3</v>
       </c>
       <c r="H157" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I157">
         <v>75</v>
@@ -5784,13 +5784,13 @@
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D158" s="4">
         <v>0.38611111111111113</v>
@@ -5806,7 +5806,7 @@
         <v>3</v>
       </c>
       <c r="H158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I158">
         <v>75</v>
@@ -5817,13 +5817,13 @@
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B159">
         <v>2</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D159" s="4">
         <v>0.43263888888888891</v>
@@ -5839,7 +5839,7 @@
         <v>3</v>
       </c>
       <c r="H159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I159">
         <v>57.5</v>
@@ -5850,13 +5850,13 @@
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B160">
         <v>3</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D160" s="4">
         <v>0.46736111111111112</v>
@@ -5872,7 +5872,7 @@
         <v>3</v>
       </c>
       <c r="H160" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I160">
         <v>65</v>
@@ -5883,13 +5883,13 @@
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B161">
         <v>4</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D161" s="4">
         <v>0.52083333333333337</v>
@@ -5905,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="H161" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I161">
         <v>82.5</v>
@@ -5916,13 +5916,13 @@
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D162" s="4">
         <v>0.3888888888888889</v>
@@ -5938,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="H162" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I162">
         <v>80</v>
@@ -5949,13 +5949,13 @@
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B163">
         <v>2</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D163" s="4">
         <v>0.44166666666666665</v>
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="H163" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I163">
         <v>75</v>
@@ -5982,13 +5982,13 @@
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B164">
         <v>3</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D164" s="4">
         <v>0.41249999999999998</v>
@@ -6004,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="H164" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I164">
         <v>75</v>
@@ -6015,13 +6015,13 @@
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B165">
         <v>4</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D165" s="4">
         <v>0.42083333333333334</v>
@@ -6037,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="H165" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I165">
         <v>75</v>
@@ -6048,13 +6048,13 @@
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D166" s="4">
         <v>0.37916666666666665</v>
@@ -6070,7 +6070,7 @@
         <v>3</v>
       </c>
       <c r="H166" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J166">
         <v>4</v>
@@ -6078,13 +6078,13 @@
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B167">
         <v>2</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D167" s="4">
         <v>0.45833333333333331</v>
@@ -6100,7 +6100,7 @@
         <v>3</v>
       </c>
       <c r="H167" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I167">
         <v>60</v>
@@ -6111,13 +6111,13 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B168">
         <v>3</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -6129,7 +6129,7 @@
         <v>3</v>
       </c>
       <c r="H168" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J168">
         <v>4</v>
@@ -6137,13 +6137,13 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D169" s="4">
         <v>0.5</v>
@@ -6159,7 +6159,7 @@
         <v>3</v>
       </c>
       <c r="H169" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I169">
         <v>57.5</v>
@@ -6170,13 +6170,13 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D170" s="4">
         <v>0.38541666666666669</v>
@@ -6192,7 +6192,7 @@
         <v>3</v>
       </c>
       <c r="H170" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I170">
         <v>42.5</v>
@@ -6203,13 +6203,13 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B171">
         <v>2</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D171" s="4">
         <v>0.44097222222222221</v>
@@ -6225,7 +6225,7 @@
         <v>3</v>
       </c>
       <c r="H171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I171">
         <v>77.5</v>
@@ -6236,13 +6236,13 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B172">
         <v>3</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D172" s="4">
         <v>0.47986111111111113</v>
@@ -6258,7 +6258,7 @@
         <v>3</v>
       </c>
       <c r="H172" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I172">
         <v>65</v>
@@ -6269,13 +6269,13 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B173">
         <v>4</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D173" s="4">
         <v>0.46666666666666667</v>
@@ -6291,7 +6291,7 @@
         <v>3</v>
       </c>
       <c r="H173" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I173">
         <v>40</v>
@@ -6302,13 +6302,13 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B174">
         <v>1</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D174" s="4">
         <v>0.38333333333333336</v>
@@ -6324,7 +6324,7 @@
         <v>3</v>
       </c>
       <c r="H174" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I174">
         <v>100</v>
@@ -6335,13 +6335,13 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B175">
         <v>2</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D175" s="4">
         <v>0.43055555555555558</v>
@@ -6357,7 +6357,7 @@
         <v>3</v>
       </c>
       <c r="H175" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I175">
         <v>100</v>
@@ -6368,13 +6368,13 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B176">
         <v>3</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D176" s="4">
         <v>0.47222222222222221</v>
@@ -6390,7 +6390,7 @@
         <v>3</v>
       </c>
       <c r="H176" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I176">
         <v>100</v>
@@ -6401,13 +6401,13 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B177">
         <v>4</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D177" s="4">
         <v>0.41319444444444442</v>
@@ -6423,7 +6423,7 @@
         <v>3</v>
       </c>
       <c r="H177" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I177">
         <v>100</v>
@@ -6434,13 +6434,13 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D178" s="4">
         <v>0.3888888888888889</v>
@@ -6456,7 +6456,7 @@
         <v>3</v>
       </c>
       <c r="H178" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I178">
         <v>95</v>
@@ -6467,13 +6467,13 @@
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B179">
         <v>2</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D179" s="4">
         <v>0.41666666666666669</v>
@@ -6489,7 +6489,7 @@
         <v>3</v>
       </c>
       <c r="H179" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I179">
         <v>75</v>
@@ -6500,13 +6500,13 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B180">
         <v>3</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D180" s="4">
         <v>0.44097222222222221</v>
@@ -6522,7 +6522,7 @@
         <v>3</v>
       </c>
       <c r="H180" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I180">
         <v>85</v>
@@ -6533,13 +6533,13 @@
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B181">
         <v>4</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D181" s="4">
         <v>0.46458333333333335</v>
@@ -6555,7 +6555,7 @@
         <v>3</v>
       </c>
       <c r="H181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I181">
         <v>55</v>
@@ -6566,13 +6566,13 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D182" s="4">
         <v>0.37986111111111109</v>
@@ -6588,7 +6588,7 @@
         <v>2</v>
       </c>
       <c r="H182" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I182">
         <v>85</v>
@@ -6599,13 +6599,13 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B183">
         <v>2</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D183" s="4">
         <v>0.44722222222222224</v>
@@ -6621,7 +6621,7 @@
         <v>2</v>
       </c>
       <c r="H183" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I183">
         <v>80</v>
@@ -6632,13 +6632,13 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B184">
         <v>3</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D184" s="4">
         <v>0.47013888888888888</v>
@@ -6654,7 +6654,7 @@
         <v>2</v>
       </c>
       <c r="H184" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I184">
         <v>70</v>
@@ -6665,13 +6665,13 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B185">
         <v>4</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D185" s="4">
         <v>0.51388888888888884</v>
@@ -6687,7 +6687,7 @@
         <v>2</v>
       </c>
       <c r="H185" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I185">
         <v>60</v>
@@ -6698,13 +6698,13 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D186" s="4">
         <v>0.39027777777777778</v>
@@ -6720,7 +6720,7 @@
         <v>3</v>
       </c>
       <c r="H186" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I186">
         <v>95</v>
@@ -6731,13 +6731,13 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B187">
         <v>2</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D187" s="4">
         <v>0.41111111111111109</v>
@@ -6753,7 +6753,7 @@
         <v>3</v>
       </c>
       <c r="H187" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I187">
         <v>100</v>
@@ -6764,13 +6764,13 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B188">
         <v>3</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D188" s="4">
         <v>0.42916666666666664</v>
@@ -6786,7 +6786,7 @@
         <v>3</v>
       </c>
       <c r="H188" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I188">
         <v>47.5</v>
@@ -6797,13 +6797,13 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B189">
         <v>4</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D189" s="4">
         <v>0.45347222222222222</v>
@@ -6819,7 +6819,7 @@
         <v>3</v>
       </c>
       <c r="H189" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I189">
         <v>37.5</v>
@@ -6830,13 +6830,13 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D190" s="4">
         <v>0.40902777777777777</v>
@@ -6852,7 +6852,7 @@
         <v>2</v>
       </c>
       <c r="H190" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I190">
         <v>97.5</v>
@@ -6863,13 +6863,13 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B191">
         <v>2</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D191" s="4">
         <v>0.44166666666666665</v>
@@ -6885,7 +6885,7 @@
         <v>2</v>
       </c>
       <c r="H191" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J191">
         <v>4</v>
@@ -6893,13 +6893,13 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B192">
         <v>3</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D192" s="4">
         <v>0.4909722222222222</v>
@@ -6915,7 +6915,7 @@
         <v>2</v>
       </c>
       <c r="H192" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J192">
         <v>3</v>
@@ -6923,13 +6923,13 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B193">
         <v>4</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D193" s="4">
         <v>0.4597222222222222</v>
@@ -6945,7 +6945,7 @@
         <v>2</v>
       </c>
       <c r="H193" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J193">
         <v>4</v>
@@ -6953,13 +6953,13 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B194">
         <v>1</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D194" s="4">
         <v>0.39930555555555558</v>
@@ -6975,7 +6975,7 @@
         <v>2</v>
       </c>
       <c r="H194" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I194">
         <v>75</v>
@@ -6986,13 +6986,13 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B195">
         <v>2</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D195" s="4">
         <v>0.4236111111111111</v>
@@ -7008,7 +7008,7 @@
         <v>2</v>
       </c>
       <c r="H195" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I195">
         <v>62.5</v>
@@ -7019,13 +7019,13 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B196">
         <v>3</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D196" s="4">
         <v>0.44097222222222221</v>
@@ -7041,7 +7041,7 @@
         <v>2</v>
       </c>
       <c r="H196" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I196">
         <v>70</v>
@@ -7052,13 +7052,13 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B197">
         <v>4</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D197" s="4">
         <v>0.46250000000000002</v>
@@ -7074,7 +7074,7 @@
         <v>2</v>
       </c>
       <c r="H197" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I197">
         <v>87.5</v>
@@ -7085,13 +7085,13 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D198" s="4">
         <v>0.3888888888888889</v>
@@ -7107,7 +7107,7 @@
         <v>3</v>
       </c>
       <c r="H198" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I198">
         <v>80</v>
@@ -7118,13 +7118,13 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B199">
         <v>2</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D199" s="4">
         <v>0.40625</v>
@@ -7140,7 +7140,7 @@
         <v>3</v>
       </c>
       <c r="H199" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I199">
         <v>32.5</v>
@@ -7151,13 +7151,13 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B200">
         <v>3</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D200" s="4">
         <v>0.43194444444444446</v>
@@ -7173,7 +7173,7 @@
         <v>3</v>
       </c>
       <c r="H200" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I200">
         <v>75</v>
@@ -7184,13 +7184,13 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B201">
         <v>4</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D201" s="4">
         <v>0.45833333333333331</v>
@@ -7206,7 +7206,7 @@
         <v>3</v>
       </c>
       <c r="H201" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I201">
         <v>30</v>
@@ -7217,13 +7217,13 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B202">
         <v>1</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D202" s="4">
         <v>0.39027777777777778</v>
@@ -7239,7 +7239,7 @@
         <v>3</v>
       </c>
       <c r="H202" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I202">
         <v>100</v>
@@ -7250,13 +7250,13 @@
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B203">
         <v>2</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D203" s="4">
         <v>0.41736111111111113</v>
@@ -7272,7 +7272,7 @@
         <v>3</v>
       </c>
       <c r="H203" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I203">
         <v>97.5</v>
@@ -7283,13 +7283,13 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B204">
         <v>3</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D204" s="4">
         <v>0.44166666666666665</v>
@@ -7305,7 +7305,7 @@
         <v>3</v>
       </c>
       <c r="H204" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I204">
         <v>100</v>
@@ -7316,13 +7316,13 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B205">
         <v>4</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D205" s="4">
         <v>0.46875</v>
@@ -7338,7 +7338,7 @@
         <v>3</v>
       </c>
       <c r="H205" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I205">
         <v>100</v>
@@ -7349,13 +7349,13 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B206">
         <v>1</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D206" s="4">
         <v>0.38750000000000001</v>
@@ -7371,7 +7371,7 @@
         <v>2</v>
       </c>
       <c r="H206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I206">
         <v>77.5</v>
@@ -7382,13 +7382,13 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B207">
         <v>2</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D207" s="4">
         <v>0.41041666666666665</v>
@@ -7404,7 +7404,7 @@
         <v>2</v>
       </c>
       <c r="H207" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I207">
         <v>72.5</v>
@@ -7415,13 +7415,13 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B208">
         <v>3</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D208" s="4">
         <v>0.4548611111111111</v>
@@ -7437,7 +7437,7 @@
         <v>2</v>
       </c>
       <c r="H208" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I208">
         <v>70</v>
@@ -7448,13 +7448,13 @@
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B209">
         <v>4</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D209" s="4">
         <v>0.47916666666666669</v>
@@ -7470,7 +7470,7 @@
         <v>2</v>
       </c>
       <c r="H209" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I209">
         <v>70</v>
@@ -7481,13 +7481,13 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B210">
         <v>1</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D210" s="4">
         <v>0.43680555555555556</v>
@@ -7503,7 +7503,7 @@
         <v>1</v>
       </c>
       <c r="H210" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J210">
         <v>4</v>
@@ -7511,13 +7511,13 @@
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B211">
         <v>2</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D211" s="4">
         <v>0.47499999999999998</v>
@@ -7533,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="H211" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I211">
         <v>77.5</v>
@@ -7544,13 +7544,13 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B212">
         <v>3</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D212" s="4">
         <v>0.48194444444444445</v>
@@ -7566,7 +7566,7 @@
         <v>1</v>
       </c>
       <c r="H212" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J212">
         <v>4</v>
@@ -7574,13 +7574,13 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B213">
         <v>4</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D213" s="4">
         <v>0.50347222222222221</v>
@@ -7596,7 +7596,7 @@
         <v>1</v>
       </c>
       <c r="H213" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J213">
         <v>4</v>
@@ -7604,13 +7604,13 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B214">
         <v>1</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D214" s="4">
         <v>0.40069444444444446</v>
@@ -7626,7 +7626,7 @@
         <v>2</v>
       </c>
       <c r="H214" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I214">
         <v>72.5</v>
@@ -7637,13 +7637,13 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B215">
         <v>2</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D215" s="4">
         <v>0.42986111111111114</v>
@@ -7659,7 +7659,7 @@
         <v>2</v>
       </c>
       <c r="H215" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J215">
         <v>3</v>
@@ -7667,13 +7667,13 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B216">
         <v>3</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D216" s="4">
         <v>0.44444444444444442</v>
@@ -7689,7 +7689,7 @@
         <v>2</v>
       </c>
       <c r="H216" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J216">
         <v>4</v>
@@ -7697,13 +7697,13 @@
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B217">
         <v>4</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D217" s="4">
         <v>0.46805555555555556</v>
@@ -7719,7 +7719,7 @@
         <v>2</v>
       </c>
       <c r="H217" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J217">
         <v>2</v>
@@ -7727,13 +7727,13 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B218">
         <v>1</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D218" s="4">
         <v>0.40277777777777779</v>
@@ -7749,7 +7749,7 @@
         <v>3</v>
       </c>
       <c r="H218" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I218">
         <v>70</v>
@@ -7760,13 +7760,13 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B219">
         <v>2</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D219" s="4">
         <v>0.44791666666666669</v>
@@ -7782,7 +7782,7 @@
         <v>3</v>
       </c>
       <c r="H219" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I219">
         <v>77.5</v>
@@ -7793,13 +7793,13 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B220">
         <v>3</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D220" s="4">
         <v>0.46180555555555558</v>
@@ -7815,7 +7815,7 @@
         <v>3</v>
       </c>
       <c r="H220" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I220">
         <v>72.5</v>
@@ -7826,13 +7826,13 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B221">
         <v>4</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D221" s="4">
         <v>0.4826388888888889</v>
@@ -7848,7 +7848,7 @@
         <v>3</v>
       </c>
       <c r="H221" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I221">
         <v>70</v>
